--- a/artfynd/A 16462-2024 artfynd.xlsx
+++ b/artfynd/A 16462-2024 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>136547885</v>
       </c>
       <c r="B4" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136540012</v>
       </c>
       <c r="B5" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136541259</v>
       </c>
       <c r="B6" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136549224</v>
       </c>
       <c r="B7" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>136547955</v>
       </c>
       <c r="B8" t="n">
-        <v>98271</v>
+        <v>98274</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16462-2024 artfynd.xlsx
+++ b/artfynd/A 16462-2024 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>136547885</v>
       </c>
       <c r="B4" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136540012</v>
       </c>
       <c r="B5" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136541259</v>
       </c>
       <c r="B6" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136549224</v>
       </c>
       <c r="B7" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>136547955</v>
       </c>
       <c r="B8" t="n">
-        <v>98274</v>
+        <v>98275</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16462-2024 artfynd.xlsx
+++ b/artfynd/A 16462-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136539491</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136542035</v>
       </c>
       <c r="B3" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136547885</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136540012</v>
       </c>
       <c r="B5" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136541259</v>
       </c>
       <c r="B6" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136549224</v>
       </c>
       <c r="B7" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>136547955</v>
       </c>
       <c r="B8" t="n">
-        <v>98275</v>
+        <v>98280</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16462-2024 artfynd.xlsx
+++ b/artfynd/A 16462-2024 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>136547885</v>
       </c>
       <c r="B4" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136540012</v>
       </c>
       <c r="B5" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136541259</v>
       </c>
       <c r="B6" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136549224</v>
       </c>
       <c r="B7" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>136547955</v>
       </c>
       <c r="B8" t="n">
-        <v>98280</v>
+        <v>98282</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16462-2024 artfynd.xlsx
+++ b/artfynd/A 16462-2024 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>136547885</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136540012</v>
       </c>
       <c r="B5" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136541259</v>
       </c>
       <c r="B6" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136549224</v>
       </c>
       <c r="B7" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>136547955</v>
       </c>
       <c r="B8" t="n">
-        <v>98282</v>
+        <v>98288</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16462-2024 artfynd.xlsx
+++ b/artfynd/A 16462-2024 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>136547885</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136540012</v>
       </c>
       <c r="B5" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136541259</v>
       </c>
       <c r="B6" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136549224</v>
       </c>
       <c r="B7" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>136547955</v>
       </c>
       <c r="B8" t="n">
-        <v>98288</v>
+        <v>98290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16462-2024 artfynd.xlsx
+++ b/artfynd/A 16462-2024 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>136547885</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136540012</v>
       </c>
       <c r="B5" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136541259</v>
       </c>
       <c r="B6" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136549224</v>
       </c>
       <c r="B7" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>136547955</v>
       </c>
       <c r="B8" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16462-2024 artfynd.xlsx
+++ b/artfynd/A 16462-2024 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>136547885</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1009,7 +1009,7 @@
         <v>136540012</v>
       </c>
       <c r="B5" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136541259</v>
       </c>
       <c r="B6" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136549224</v>
       </c>
       <c r="B7" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>136547955</v>
       </c>
       <c r="B8" t="n">
-        <v>98291</v>
+        <v>98297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16462-2024 artfynd.xlsx
+++ b/artfynd/A 16462-2024 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>136547885</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1009,7 +1009,7 @@
         <v>136540012</v>
       </c>
       <c r="B5" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136541259</v>
       </c>
       <c r="B6" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136549224</v>
       </c>
       <c r="B7" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>136547955</v>
       </c>
       <c r="B8" t="n">
-        <v>98297</v>
+        <v>98301</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16462-2024 artfynd.xlsx
+++ b/artfynd/A 16462-2024 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>136547885</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136540012</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136541259</v>
       </c>
       <c r="B6" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136549224</v>
       </c>
       <c r="B7" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>136547955</v>
       </c>
       <c r="B8" t="n">
-        <v>98301</v>
+        <v>98303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16462-2024 artfynd.xlsx
+++ b/artfynd/A 16462-2024 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>136547885</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1009,7 +1009,7 @@
         <v>136540012</v>
       </c>
       <c r="B5" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136541259</v>
       </c>
       <c r="B6" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136549224</v>
       </c>
       <c r="B7" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>136547955</v>
       </c>
       <c r="B8" t="n">
-        <v>98303</v>
+        <v>98305</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16462-2024 artfynd.xlsx
+++ b/artfynd/A 16462-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136539491</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136542035</v>
       </c>
       <c r="B3" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136547885</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1009,7 +1009,7 @@
         <v>136540012</v>
       </c>
       <c r="B5" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136541259</v>
       </c>
       <c r="B6" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136549224</v>
       </c>
       <c r="B7" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>136547955</v>
       </c>
       <c r="B8" t="n">
-        <v>98305</v>
+        <v>98318</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16462-2024 artfynd.xlsx
+++ b/artfynd/A 16462-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136539491</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136542035</v>
       </c>
       <c r="B3" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136547885</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136540012</v>
       </c>
       <c r="B5" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136541259</v>
       </c>
       <c r="B6" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136549224</v>
       </c>
       <c r="B7" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>136547955</v>
       </c>
       <c r="B8" t="n">
-        <v>98318</v>
+        <v>98320</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
